--- a/assets/portfolio/International Diversification.xlsx
+++ b/assets/portfolio/International Diversification.xlsx
@@ -1,66 +1,66 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="21126"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="23127"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\pdwho\Dropbox\Courses\Teaching\FIN 203\FIN 203 Spring 2019\2 Portfolio Theory\2 Exercises\2 International Diversification\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\pdwho\Dropbox (Personal)\Courses\Teaching\FIN 203\FIN 203 Fall 2020\2 Portfolio Theory\2 Exercises\2 International Diversification\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2EB17255-E4DE-48E5-9A25-57BEAC3A8F7B}" xr6:coauthVersionLast="40" xr6:coauthVersionMax="40" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ECF6A3DF-D4EC-4B53-A989-9EC475E23FB3}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="9024" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Info" sheetId="2" r:id="rId1"/>
-    <sheet name="Questions" sheetId="3" r:id="rId2"/>
-    <sheet name="Data" sheetId="1" r:id="rId3"/>
+    <sheet name="Data" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="solver_adj" localSheetId="2" hidden="1">Data!$O$5:$U$5</definedName>
-    <definedName name="solver_cvg" localSheetId="2" hidden="1">0.0001</definedName>
-    <definedName name="solver_drv" localSheetId="2" hidden="1">1</definedName>
-    <definedName name="solver_eng" localSheetId="2" hidden="1">1</definedName>
-    <definedName name="solver_est" localSheetId="2" hidden="1">1</definedName>
-    <definedName name="solver_itr" localSheetId="2" hidden="1">2147483647</definedName>
-    <definedName name="solver_lhs1" localSheetId="2" hidden="1">Data!$O$5:$U$5</definedName>
-    <definedName name="solver_lhs2" localSheetId="2" hidden="1">Data!$O$5:$U$5</definedName>
-    <definedName name="solver_lhs3" localSheetId="2" hidden="1">Data!$V$5</definedName>
-    <definedName name="solver_mip" localSheetId="2" hidden="1">2147483647</definedName>
-    <definedName name="solver_mni" localSheetId="2" hidden="1">30</definedName>
-    <definedName name="solver_mrt" localSheetId="2" hidden="1">0.075</definedName>
-    <definedName name="solver_msl" localSheetId="2" hidden="1">2</definedName>
-    <definedName name="solver_neg" localSheetId="2" hidden="1">2</definedName>
-    <definedName name="solver_nod" localSheetId="2" hidden="1">2147483647</definedName>
-    <definedName name="solver_num" localSheetId="2" hidden="1">3</definedName>
-    <definedName name="solver_nwt" localSheetId="2" hidden="1">1</definedName>
-    <definedName name="solver_opt" localSheetId="2" hidden="1">Data!$V$4</definedName>
-    <definedName name="solver_pre" localSheetId="2" hidden="1">0.000001</definedName>
-    <definedName name="solver_rbv" localSheetId="2" hidden="1">1</definedName>
-    <definedName name="solver_rel1" localSheetId="2" hidden="1">1</definedName>
-    <definedName name="solver_rel2" localSheetId="2" hidden="1">3</definedName>
-    <definedName name="solver_rel3" localSheetId="2" hidden="1">2</definedName>
-    <definedName name="solver_rhs1" localSheetId="2" hidden="1">1</definedName>
-    <definedName name="solver_rhs2" localSheetId="2" hidden="1">0</definedName>
-    <definedName name="solver_rhs3" localSheetId="2" hidden="1">1</definedName>
-    <definedName name="solver_rlx" localSheetId="2" hidden="1">2</definedName>
-    <definedName name="solver_rsd" localSheetId="2" hidden="1">0</definedName>
-    <definedName name="solver_scl" localSheetId="2" hidden="1">1</definedName>
-    <definedName name="solver_sho" localSheetId="2" hidden="1">2</definedName>
-    <definedName name="solver_ssz" localSheetId="2" hidden="1">100</definedName>
-    <definedName name="solver_tim" localSheetId="2" hidden="1">2147483647</definedName>
-    <definedName name="solver_tol" localSheetId="2" hidden="1">0.01</definedName>
-    <definedName name="solver_typ" localSheetId="2" hidden="1">1</definedName>
-    <definedName name="solver_val" localSheetId="2" hidden="1">0</definedName>
-    <definedName name="solver_ver" localSheetId="2" hidden="1">3</definedName>
+    <definedName name="solver_adj" localSheetId="0" hidden="1">Data!$O$5:$U$5</definedName>
+    <definedName name="solver_cvg" localSheetId="0" hidden="1">0.0001</definedName>
+    <definedName name="solver_drv" localSheetId="0" hidden="1">1</definedName>
+    <definedName name="solver_eng" localSheetId="0" hidden="1">1</definedName>
+    <definedName name="solver_est" localSheetId="0" hidden="1">1</definedName>
+    <definedName name="solver_itr" localSheetId="0" hidden="1">2147483647</definedName>
+    <definedName name="solver_lhs1" localSheetId="0" hidden="1">Data!$O$5:$U$5</definedName>
+    <definedName name="solver_lhs2" localSheetId="0" hidden="1">Data!$O$5:$U$5</definedName>
+    <definedName name="solver_lhs3" localSheetId="0" hidden="1">Data!$V$5</definedName>
+    <definedName name="solver_mip" localSheetId="0" hidden="1">2147483647</definedName>
+    <definedName name="solver_mni" localSheetId="0" hidden="1">30</definedName>
+    <definedName name="solver_mrt" localSheetId="0" hidden="1">0.075</definedName>
+    <definedName name="solver_msl" localSheetId="0" hidden="1">2</definedName>
+    <definedName name="solver_neg" localSheetId="0" hidden="1">2</definedName>
+    <definedName name="solver_nod" localSheetId="0" hidden="1">2147483647</definedName>
+    <definedName name="solver_num" localSheetId="0" hidden="1">3</definedName>
+    <definedName name="solver_nwt" localSheetId="0" hidden="1">1</definedName>
+    <definedName name="solver_opt" localSheetId="0" hidden="1">Data!$V$4</definedName>
+    <definedName name="solver_pre" localSheetId="0" hidden="1">0.000001</definedName>
+    <definedName name="solver_rbv" localSheetId="0" hidden="1">1</definedName>
+    <definedName name="solver_rel1" localSheetId="0" hidden="1">1</definedName>
+    <definedName name="solver_rel2" localSheetId="0" hidden="1">3</definedName>
+    <definedName name="solver_rel3" localSheetId="0" hidden="1">2</definedName>
+    <definedName name="solver_rhs1" localSheetId="0" hidden="1">1</definedName>
+    <definedName name="solver_rhs2" localSheetId="0" hidden="1">0</definedName>
+    <definedName name="solver_rhs3" localSheetId="0" hidden="1">1</definedName>
+    <definedName name="solver_rlx" localSheetId="0" hidden="1">2</definedName>
+    <definedName name="solver_rsd" localSheetId="0" hidden="1">0</definedName>
+    <definedName name="solver_scl" localSheetId="0" hidden="1">1</definedName>
+    <definedName name="solver_sho" localSheetId="0" hidden="1">2</definedName>
+    <definedName name="solver_ssz" localSheetId="0" hidden="1">100</definedName>
+    <definedName name="solver_tim" localSheetId="0" hidden="1">2147483647</definedName>
+    <definedName name="solver_tol" localSheetId="0" hidden="1">0.01</definedName>
+    <definedName name="solver_typ" localSheetId="0" hidden="1">1</definedName>
+    <definedName name="solver_val" localSheetId="0" hidden="1">0</definedName>
+    <definedName name="solver_ver" localSheetId="0" hidden="1">3</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
         <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
         <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
       </xcalcf:calcFeatures>
     </ext>
   </extLst>
@@ -68,7 +68,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="15">
   <si>
     <t>US</t>
   </si>
@@ -114,33 +114,6 @@
   <si>
     <t>Correlation</t>
   </si>
-  <si>
-    <t>Assignment</t>
-  </si>
-  <si>
-    <t>Industry Returns</t>
-  </si>
-  <si>
-    <t>First Name</t>
-  </si>
-  <si>
-    <t>Last Name</t>
-  </si>
-  <si>
-    <t>WFU User Name</t>
-  </si>
-  <si>
-    <t>Email</t>
-  </si>
-  <si>
-    <t>Class Section</t>
-  </si>
-  <si>
-    <t>1. What are the optimal investment weights for Japan and the US?</t>
-  </si>
-  <si>
-    <t>1. Explain the economic reasoning for why Solver choose these specific optimal investment weights.</t>
-  </si>
 </sst>
 </file>
 
@@ -150,7 +123,7 @@
     <numFmt numFmtId="164" formatCode="mm/yy"/>
     <numFmt numFmtId="165" formatCode="0.0"/>
   </numFmts>
-  <fonts count="21" x14ac:knownFonts="1">
+  <fonts count="19" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -290,21 +263,8 @@
       <name val="Arial"/>
       <family val="2"/>
     </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
   </fonts>
-  <fills count="35">
+  <fills count="34">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -490,12 +450,6 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.79998168889431442"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
   </fills>
   <borders count="10">
     <border>
@@ -659,7 +613,7 @@
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -671,31 +625,6 @@
     <xf numFmtId="2" fontId="0" fillId="33" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="9" fontId="0" fillId="33" borderId="0" xfId="43" applyFont="1" applyFill="1"/>
     <xf numFmtId="2" fontId="0" fillId="33" borderId="0" xfId="43" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1"/>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyProtection="1"/>
-    <xf numFmtId="0" fontId="20" fillId="34" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="34" borderId="0" xfId="0" applyFill="1" applyProtection="1">
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="34" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="top" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
   </cellXfs>
   <cellStyles count="44">
     <cellStyle name="20% - Accent1" xfId="19" builtinId="30" customBuiltin="1"/>
@@ -1052,146 +981,31 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0A6E7FD0-F0B2-4D60-98C0-2EE9E816C662}">
-  <dimension ref="A1:B6"/>
-  <sheetFormatPr defaultColWidth="8.6484375" defaultRowHeight="15.6" x14ac:dyDescent="0.6"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:V445"/>
+  <sheetFormatPr defaultRowHeight="15.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="13.34765625" style="13" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="13.5" style="13" bestFit="1" customWidth="1"/>
-    <col min="3" max="16384" width="8.6484375" style="13"/>
+    <col min="1" max="1" width="5.6640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="3" width="5" style="2" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="7.1640625" style="2" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="6.4140625" style="2" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="8.5" style="2" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="5" style="2" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="5.83203125" style="2" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="8.33203125" style="2" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="12.5" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="4.4140625" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="10.4140625" bestFit="1" customWidth="1"/>
+    <col min="15" max="16" width="4.4140625" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="7.1640625" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="6.4140625" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="8.5" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="4.5" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="5.83203125" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="8.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.6">
-      <c r="A1" s="11" t="s">
-        <v>15</v>
-      </c>
-      <c r="B1" s="12" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.6">
-      <c r="A2" s="11" t="s">
-        <v>17</v>
-      </c>
-      <c r="B2" s="14"/>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.6">
-      <c r="A3" s="11" t="s">
-        <v>18</v>
-      </c>
-      <c r="B3" s="14"/>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.6">
-      <c r="A4" s="11" t="s">
-        <v>19</v>
-      </c>
-      <c r="B4" s="14"/>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.6">
-      <c r="A5" s="11" t="s">
-        <v>20</v>
-      </c>
-      <c r="B5" s="14"/>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.6">
-      <c r="A6" s="11" t="s">
-        <v>21</v>
-      </c>
-      <c r="B6" s="15"/>
-    </row>
-  </sheetData>
-  <sheetProtection sheet="1" selectLockedCells="1"/>
-  <protectedRanges>
-    <protectedRange sqref="B2:B6" name="Range1"/>
-  </protectedRanges>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{44E79080-4DB9-4E64-B481-54A2950583E8}">
-  <dimension ref="A1:H10"/>
-  <sheetFormatPr defaultColWidth="8.6484375" defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
-  <cols>
-    <col min="1" max="2" width="48.59765625" style="17" customWidth="1"/>
-    <col min="3" max="16384" width="8.6484375" style="17"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:8" ht="48" customHeight="1" x14ac:dyDescent="0.6">
-      <c r="A1" s="20" t="s">
-        <v>22</v>
-      </c>
-      <c r="B1" s="16"/>
-    </row>
-    <row r="2" spans="1:8" ht="48" customHeight="1" x14ac:dyDescent="0.6">
-      <c r="A2" s="20" t="s">
-        <v>23</v>
-      </c>
-      <c r="B2" s="16"/>
-    </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.55000000000000004">
-      <c r="A7" s="18"/>
-    </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.55000000000000004">
-      <c r="C8" s="19"/>
-      <c r="D8" s="19"/>
-      <c r="E8" s="19"/>
-      <c r="F8" s="19"/>
-      <c r="G8" s="19"/>
-      <c r="H8" s="19"/>
-    </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.55000000000000004">
-      <c r="C9" s="19"/>
-      <c r="D9" s="19"/>
-      <c r="E9" s="19"/>
-      <c r="F9" s="19"/>
-      <c r="G9" s="19"/>
-      <c r="H9" s="19"/>
-    </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.55000000000000004">
-      <c r="A10" s="19"/>
-      <c r="B10" s="19"/>
-      <c r="C10" s="19"/>
-      <c r="D10" s="19"/>
-      <c r="E10" s="19"/>
-      <c r="F10" s="19"/>
-      <c r="G10" s="19"/>
-      <c r="H10" s="19"/>
-    </row>
-  </sheetData>
-  <sheetProtection sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:V445"/>
-  <sheetFormatPr defaultRowHeight="15.6" x14ac:dyDescent="0.6"/>
-  <cols>
-    <col min="1" max="1" width="5.69921875" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="3" width="5" style="2" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="7.19921875" style="2" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="6.3984375" style="2" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="8.5" style="2" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="5" style="2" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="5.796875" style="2" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="8.296875" style="2" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="12.5" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="4.3984375" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="10.3984375" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="4.3984375" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="7.19921875" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="6.3984375" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="8.5" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="4.5" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="5.796875" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="8.296875" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:22" x14ac:dyDescent="0.6">
+    <row r="1" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A1" s="5" t="s">
         <v>1</v>
       </c>
@@ -1244,7 +1058,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:22" x14ac:dyDescent="0.6">
+    <row r="2" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A2" s="1">
         <v>28126</v>
       </c>
@@ -1289,7 +1103,7 @@
       <c r="U2" s="7"/>
       <c r="V2" s="7"/>
     </row>
-    <row r="3" spans="1:22" x14ac:dyDescent="0.6">
+    <row r="3" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A3" s="1">
         <v>28157</v>
       </c>
@@ -1327,7 +1141,7 @@
       <c r="U3" s="7"/>
       <c r="V3" s="7"/>
     </row>
-    <row r="4" spans="1:22" x14ac:dyDescent="0.6">
+    <row r="4" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A4" s="1">
         <v>28185</v>
       </c>
@@ -1365,7 +1179,7 @@
       <c r="U4" s="8"/>
       <c r="V4" s="8"/>
     </row>
-    <row r="5" spans="1:22" x14ac:dyDescent="0.6">
+    <row r="5" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A5" s="1">
         <v>28216</v>
       </c>
@@ -1403,7 +1217,7 @@
       <c r="U5" s="9"/>
       <c r="V5" s="9"/>
     </row>
-    <row r="6" spans="1:22" x14ac:dyDescent="0.6">
+    <row r="6" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A6" s="1">
         <v>28246</v>
       </c>
@@ -1430,7 +1244,7 @@
       </c>
       <c r="I6" s="7"/>
     </row>
-    <row r="7" spans="1:22" x14ac:dyDescent="0.6">
+    <row r="7" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A7" s="1">
         <v>28277</v>
       </c>
@@ -1484,7 +1298,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="8" spans="1:22" x14ac:dyDescent="0.6">
+    <row r="8" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A8" s="1">
         <v>28307</v>
       </c>
@@ -1522,7 +1336,7 @@
       <c r="U8" s="10"/>
       <c r="V8" s="10"/>
     </row>
-    <row r="9" spans="1:22" x14ac:dyDescent="0.6">
+    <row r="9" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A9" s="1">
         <v>28338</v>
       </c>
@@ -1560,7 +1374,7 @@
       <c r="U9" s="10"/>
       <c r="V9" s="10"/>
     </row>
-    <row r="10" spans="1:22" x14ac:dyDescent="0.6">
+    <row r="10" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A10" s="1">
         <v>28369</v>
       </c>
@@ -1598,7 +1412,7 @@
       <c r="U10" s="10"/>
       <c r="V10" s="10"/>
     </row>
-    <row r="11" spans="1:22" x14ac:dyDescent="0.6">
+    <row r="11" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A11" s="1">
         <v>28399</v>
       </c>
@@ -1636,7 +1450,7 @@
       <c r="U11" s="10"/>
       <c r="V11" s="10"/>
     </row>
-    <row r="12" spans="1:22" x14ac:dyDescent="0.6">
+    <row r="12" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A12" s="1">
         <v>28430</v>
       </c>
@@ -1674,7 +1488,7 @@
       <c r="U12" s="10"/>
       <c r="V12" s="10"/>
     </row>
-    <row r="13" spans="1:22" x14ac:dyDescent="0.6">
+    <row r="13" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A13" s="1">
         <v>28460</v>
       </c>
@@ -1712,7 +1526,7 @@
       <c r="U13" s="10"/>
       <c r="V13" s="10"/>
     </row>
-    <row r="14" spans="1:22" x14ac:dyDescent="0.6">
+    <row r="14" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A14" s="1">
         <v>28491</v>
       </c>
@@ -1750,7 +1564,7 @@
       <c r="U14" s="10"/>
       <c r="V14" s="10"/>
     </row>
-    <row r="15" spans="1:22" x14ac:dyDescent="0.6">
+    <row r="15" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A15" s="1">
         <v>28522</v>
       </c>
@@ -1788,7 +1602,7 @@
       <c r="U15" s="10"/>
       <c r="V15" s="10"/>
     </row>
-    <row r="16" spans="1:22" x14ac:dyDescent="0.6">
+    <row r="16" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A16" s="1">
         <v>28550</v>
       </c>
@@ -1815,7 +1629,7 @@
       </c>
       <c r="I16" s="7"/>
     </row>
-    <row r="17" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="17" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A17" s="1">
         <v>28581</v>
       </c>
@@ -1842,7 +1656,7 @@
       </c>
       <c r="I17" s="7"/>
     </row>
-    <row r="18" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="18" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A18" s="1">
         <v>28611</v>
       </c>
@@ -1869,7 +1683,7 @@
       </c>
       <c r="I18" s="7"/>
     </row>
-    <row r="19" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="19" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A19" s="1">
         <v>28642</v>
       </c>
@@ -1896,7 +1710,7 @@
       </c>
       <c r="I19" s="7"/>
     </row>
-    <row r="20" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="20" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A20" s="1">
         <v>28672</v>
       </c>
@@ -1923,7 +1737,7 @@
       </c>
       <c r="I20" s="7"/>
     </row>
-    <row r="21" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="21" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A21" s="1">
         <v>28703</v>
       </c>
@@ -1950,7 +1764,7 @@
       </c>
       <c r="I21" s="7"/>
     </row>
-    <row r="22" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="22" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A22" s="1">
         <v>28734</v>
       </c>
@@ -1977,7 +1791,7 @@
       </c>
       <c r="I22" s="7"/>
     </row>
-    <row r="23" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="23" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A23" s="1">
         <v>28764</v>
       </c>
@@ -2004,7 +1818,7 @@
       </c>
       <c r="I23" s="7"/>
     </row>
-    <row r="24" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="24" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A24" s="1">
         <v>28795</v>
       </c>
@@ -2031,7 +1845,7 @@
       </c>
       <c r="I24" s="7"/>
     </row>
-    <row r="25" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="25" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A25" s="1">
         <v>28825</v>
       </c>
@@ -2058,7 +1872,7 @@
       </c>
       <c r="I25" s="7"/>
     </row>
-    <row r="26" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="26" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A26" s="1">
         <v>28856</v>
       </c>
@@ -2085,7 +1899,7 @@
       </c>
       <c r="I26" s="7"/>
     </row>
-    <row r="27" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="27" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A27" s="1">
         <v>28887</v>
       </c>
@@ -2112,7 +1926,7 @@
       </c>
       <c r="I27" s="7"/>
     </row>
-    <row r="28" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="28" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A28" s="1">
         <v>28915</v>
       </c>
@@ -2139,7 +1953,7 @@
       </c>
       <c r="I28" s="7"/>
     </row>
-    <row r="29" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="29" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A29" s="1">
         <v>28946</v>
       </c>
@@ -2166,7 +1980,7 @@
       </c>
       <c r="I29" s="7"/>
     </row>
-    <row r="30" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="30" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A30" s="1">
         <v>28976</v>
       </c>
@@ -2193,7 +2007,7 @@
       </c>
       <c r="I30" s="7"/>
     </row>
-    <row r="31" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="31" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A31" s="1">
         <v>29007</v>
       </c>
@@ -2220,7 +2034,7 @@
       </c>
       <c r="I31" s="7"/>
     </row>
-    <row r="32" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="32" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A32" s="1">
         <v>29037</v>
       </c>
@@ -2247,7 +2061,7 @@
       </c>
       <c r="I32" s="7"/>
     </row>
-    <row r="33" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="33" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A33" s="1">
         <v>29068</v>
       </c>
@@ -2274,7 +2088,7 @@
       </c>
       <c r="I33" s="7"/>
     </row>
-    <row r="34" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="34" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A34" s="1">
         <v>29099</v>
       </c>
@@ -2301,7 +2115,7 @@
       </c>
       <c r="I34" s="7"/>
     </row>
-    <row r="35" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="35" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A35" s="1">
         <v>29129</v>
       </c>
@@ -2328,7 +2142,7 @@
       </c>
       <c r="I35" s="7"/>
     </row>
-    <row r="36" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="36" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A36" s="1">
         <v>29160</v>
       </c>
@@ -2355,7 +2169,7 @@
       </c>
       <c r="I36" s="7"/>
     </row>
-    <row r="37" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="37" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A37" s="1">
         <v>29190</v>
       </c>
@@ -2382,7 +2196,7 @@
       </c>
       <c r="I37" s="7"/>
     </row>
-    <row r="38" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="38" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A38" s="1">
         <v>29221</v>
       </c>
@@ -2409,7 +2223,7 @@
       </c>
       <c r="I38" s="7"/>
     </row>
-    <row r="39" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="39" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A39" s="1">
         <v>29252</v>
       </c>
@@ -2436,7 +2250,7 @@
       </c>
       <c r="I39" s="7"/>
     </row>
-    <row r="40" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="40" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A40" s="1">
         <v>29281</v>
       </c>
@@ -2463,7 +2277,7 @@
       </c>
       <c r="I40" s="7"/>
     </row>
-    <row r="41" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="41" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A41" s="1">
         <v>29312</v>
       </c>
@@ -2490,7 +2304,7 @@
       </c>
       <c r="I41" s="7"/>
     </row>
-    <row r="42" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="42" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A42" s="1">
         <v>29342</v>
       </c>
@@ -2517,7 +2331,7 @@
       </c>
       <c r="I42" s="7"/>
     </row>
-    <row r="43" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="43" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A43" s="1">
         <v>29373</v>
       </c>
@@ -2544,7 +2358,7 @@
       </c>
       <c r="I43" s="7"/>
     </row>
-    <row r="44" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="44" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A44" s="1">
         <v>29403</v>
       </c>
@@ -2571,7 +2385,7 @@
       </c>
       <c r="I44" s="7"/>
     </row>
-    <row r="45" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="45" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A45" s="1">
         <v>29434</v>
       </c>
@@ -2598,7 +2412,7 @@
       </c>
       <c r="I45" s="7"/>
     </row>
-    <row r="46" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="46" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A46" s="1">
         <v>29465</v>
       </c>
@@ -2625,7 +2439,7 @@
       </c>
       <c r="I46" s="7"/>
     </row>
-    <row r="47" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="47" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A47" s="1">
         <v>29495</v>
       </c>
@@ -2652,7 +2466,7 @@
       </c>
       <c r="I47" s="7"/>
     </row>
-    <row r="48" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="48" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A48" s="1">
         <v>29526</v>
       </c>
@@ -2679,7 +2493,7 @@
       </c>
       <c r="I48" s="7"/>
     </row>
-    <row r="49" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="49" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A49" s="1">
         <v>29556</v>
       </c>
@@ -2706,7 +2520,7 @@
       </c>
       <c r="I49" s="7"/>
     </row>
-    <row r="50" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="50" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A50" s="1">
         <v>29587</v>
       </c>
@@ -2733,7 +2547,7 @@
       </c>
       <c r="I50" s="7"/>
     </row>
-    <row r="51" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="51" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A51" s="1">
         <v>29618</v>
       </c>
@@ -2760,7 +2574,7 @@
       </c>
       <c r="I51" s="7"/>
     </row>
-    <row r="52" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="52" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A52" s="1">
         <v>29646</v>
       </c>
@@ -2787,7 +2601,7 @@
       </c>
       <c r="I52" s="7"/>
     </row>
-    <row r="53" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="53" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A53" s="1">
         <v>29677</v>
       </c>
@@ -2814,7 +2628,7 @@
       </c>
       <c r="I53" s="7"/>
     </row>
-    <row r="54" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="54" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A54" s="1">
         <v>29707</v>
       </c>
@@ -2841,7 +2655,7 @@
       </c>
       <c r="I54" s="7"/>
     </row>
-    <row r="55" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="55" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A55" s="1">
         <v>29738</v>
       </c>
@@ -2868,7 +2682,7 @@
       </c>
       <c r="I55" s="7"/>
     </row>
-    <row r="56" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="56" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A56" s="1">
         <v>29768</v>
       </c>
@@ -2895,7 +2709,7 @@
       </c>
       <c r="I56" s="7"/>
     </row>
-    <row r="57" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="57" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A57" s="1">
         <v>29799</v>
       </c>
@@ -2922,7 +2736,7 @@
       </c>
       <c r="I57" s="7"/>
     </row>
-    <row r="58" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="58" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A58" s="1">
         <v>29830</v>
       </c>
@@ -2949,7 +2763,7 @@
       </c>
       <c r="I58" s="7"/>
     </row>
-    <row r="59" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="59" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A59" s="1">
         <v>29860</v>
       </c>
@@ -2976,7 +2790,7 @@
       </c>
       <c r="I59" s="7"/>
     </row>
-    <row r="60" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="60" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A60" s="1">
         <v>29891</v>
       </c>
@@ -3003,7 +2817,7 @@
       </c>
       <c r="I60" s="7"/>
     </row>
-    <row r="61" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="61" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A61" s="1">
         <v>29921</v>
       </c>
@@ -3030,7 +2844,7 @@
       </c>
       <c r="I61" s="7"/>
     </row>
-    <row r="62" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="62" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A62" s="1">
         <v>29952</v>
       </c>
@@ -3057,7 +2871,7 @@
       </c>
       <c r="I62" s="7"/>
     </row>
-    <row r="63" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="63" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A63" s="1">
         <v>29983</v>
       </c>
@@ -3084,7 +2898,7 @@
       </c>
       <c r="I63" s="7"/>
     </row>
-    <row r="64" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="64" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A64" s="1">
         <v>30011</v>
       </c>
@@ -3111,7 +2925,7 @@
       </c>
       <c r="I64" s="7"/>
     </row>
-    <row r="65" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="65" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A65" s="1">
         <v>30042</v>
       </c>
@@ -3138,7 +2952,7 @@
       </c>
       <c r="I65" s="7"/>
     </row>
-    <row r="66" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="66" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A66" s="1">
         <v>30072</v>
       </c>
@@ -3165,7 +2979,7 @@
       </c>
       <c r="I66" s="7"/>
     </row>
-    <row r="67" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="67" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A67" s="1">
         <v>30103</v>
       </c>
@@ -3192,7 +3006,7 @@
       </c>
       <c r="I67" s="7"/>
     </row>
-    <row r="68" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="68" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A68" s="1">
         <v>30133</v>
       </c>
@@ -3219,7 +3033,7 @@
       </c>
       <c r="I68" s="7"/>
     </row>
-    <row r="69" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="69" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A69" s="1">
         <v>30164</v>
       </c>
@@ -3246,7 +3060,7 @@
       </c>
       <c r="I69" s="7"/>
     </row>
-    <row r="70" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="70" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A70" s="1">
         <v>30195</v>
       </c>
@@ -3273,7 +3087,7 @@
       </c>
       <c r="I70" s="7"/>
     </row>
-    <row r="71" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="71" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A71" s="1">
         <v>30225</v>
       </c>
@@ -3300,7 +3114,7 @@
       </c>
       <c r="I71" s="7"/>
     </row>
-    <row r="72" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="72" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A72" s="1">
         <v>30256</v>
       </c>
@@ -3327,7 +3141,7 @@
       </c>
       <c r="I72" s="7"/>
     </row>
-    <row r="73" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="73" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A73" s="1">
         <v>30286</v>
       </c>
@@ -3354,7 +3168,7 @@
       </c>
       <c r="I73" s="7"/>
     </row>
-    <row r="74" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="74" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A74" s="1">
         <v>30317</v>
       </c>
@@ -3381,7 +3195,7 @@
       </c>
       <c r="I74" s="7"/>
     </row>
-    <row r="75" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="75" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A75" s="1">
         <v>30348</v>
       </c>
@@ -3408,7 +3222,7 @@
       </c>
       <c r="I75" s="7"/>
     </row>
-    <row r="76" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="76" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A76" s="1">
         <v>30376</v>
       </c>
@@ -3435,7 +3249,7 @@
       </c>
       <c r="I76" s="7"/>
     </row>
-    <row r="77" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="77" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A77" s="1">
         <v>30407</v>
       </c>
@@ -3462,7 +3276,7 @@
       </c>
       <c r="I77" s="7"/>
     </row>
-    <row r="78" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="78" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A78" s="1">
         <v>30437</v>
       </c>
@@ -3489,7 +3303,7 @@
       </c>
       <c r="I78" s="7"/>
     </row>
-    <row r="79" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="79" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A79" s="1">
         <v>30468</v>
       </c>
@@ -3516,7 +3330,7 @@
       </c>
       <c r="I79" s="7"/>
     </row>
-    <row r="80" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="80" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A80" s="1">
         <v>30498</v>
       </c>
@@ -3543,7 +3357,7 @@
       </c>
       <c r="I80" s="7"/>
     </row>
-    <row r="81" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="81" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A81" s="1">
         <v>30529</v>
       </c>
@@ -3570,7 +3384,7 @@
       </c>
       <c r="I81" s="7"/>
     </row>
-    <row r="82" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="82" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A82" s="1">
         <v>30560</v>
       </c>
@@ -3597,7 +3411,7 @@
       </c>
       <c r="I82" s="7"/>
     </row>
-    <row r="83" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="83" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A83" s="1">
         <v>30590</v>
       </c>
@@ -3624,7 +3438,7 @@
       </c>
       <c r="I83" s="7"/>
     </row>
-    <row r="84" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="84" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A84" s="1">
         <v>30621</v>
       </c>
@@ -3651,7 +3465,7 @@
       </c>
       <c r="I84" s="7"/>
     </row>
-    <row r="85" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="85" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A85" s="1">
         <v>30651</v>
       </c>
@@ -3678,7 +3492,7 @@
       </c>
       <c r="I85" s="7"/>
     </row>
-    <row r="86" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="86" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A86" s="1">
         <v>30682</v>
       </c>
@@ -3705,7 +3519,7 @@
       </c>
       <c r="I86" s="7"/>
     </row>
-    <row r="87" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="87" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A87" s="1">
         <v>30713</v>
       </c>
@@ -3732,7 +3546,7 @@
       </c>
       <c r="I87" s="7"/>
     </row>
-    <row r="88" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="88" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A88" s="1">
         <v>30742</v>
       </c>
@@ -3759,7 +3573,7 @@
       </c>
       <c r="I88" s="7"/>
     </row>
-    <row r="89" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="89" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A89" s="1">
         <v>30773</v>
       </c>
@@ -3786,7 +3600,7 @@
       </c>
       <c r="I89" s="7"/>
     </row>
-    <row r="90" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="90" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A90" s="1">
         <v>30803</v>
       </c>
@@ -3813,7 +3627,7 @@
       </c>
       <c r="I90" s="7"/>
     </row>
-    <row r="91" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="91" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A91" s="1">
         <v>30834</v>
       </c>
@@ -3840,7 +3654,7 @@
       </c>
       <c r="I91" s="7"/>
     </row>
-    <row r="92" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="92" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A92" s="1">
         <v>30864</v>
       </c>
@@ -3867,7 +3681,7 @@
       </c>
       <c r="I92" s="7"/>
     </row>
-    <row r="93" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="93" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A93" s="1">
         <v>30895</v>
       </c>
@@ -3894,7 +3708,7 @@
       </c>
       <c r="I93" s="7"/>
     </row>
-    <row r="94" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="94" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A94" s="1">
         <v>30926</v>
       </c>
@@ -3921,7 +3735,7 @@
       </c>
       <c r="I94" s="7"/>
     </row>
-    <row r="95" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="95" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A95" s="1">
         <v>30956</v>
       </c>
@@ -3948,7 +3762,7 @@
       </c>
       <c r="I95" s="7"/>
     </row>
-    <row r="96" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="96" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A96" s="1">
         <v>30987</v>
       </c>
@@ -3975,7 +3789,7 @@
       </c>
       <c r="I96" s="7"/>
     </row>
-    <row r="97" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="97" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A97" s="1">
         <v>31017</v>
       </c>
@@ -4002,7 +3816,7 @@
       </c>
       <c r="I97" s="7"/>
     </row>
-    <row r="98" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="98" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A98" s="1">
         <v>31048</v>
       </c>
@@ -4029,7 +3843,7 @@
       </c>
       <c r="I98" s="7"/>
     </row>
-    <row r="99" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="99" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A99" s="1">
         <v>31079</v>
       </c>
@@ -4056,7 +3870,7 @@
       </c>
       <c r="I99" s="7"/>
     </row>
-    <row r="100" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="100" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A100" s="1">
         <v>31107</v>
       </c>
@@ -4083,7 +3897,7 @@
       </c>
       <c r="I100" s="7"/>
     </row>
-    <row r="101" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="101" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A101" s="1">
         <v>31138</v>
       </c>
@@ -4110,7 +3924,7 @@
       </c>
       <c r="I101" s="7"/>
     </row>
-    <row r="102" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="102" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A102" s="1">
         <v>31168</v>
       </c>
@@ -4137,7 +3951,7 @@
       </c>
       <c r="I102" s="7"/>
     </row>
-    <row r="103" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="103" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A103" s="1">
         <v>31199</v>
       </c>
@@ -4164,7 +3978,7 @@
       </c>
       <c r="I103" s="7"/>
     </row>
-    <row r="104" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="104" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A104" s="1">
         <v>31229</v>
       </c>
@@ -4191,7 +4005,7 @@
       </c>
       <c r="I104" s="7"/>
     </row>
-    <row r="105" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="105" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A105" s="1">
         <v>31260</v>
       </c>
@@ -4218,7 +4032,7 @@
       </c>
       <c r="I105" s="7"/>
     </row>
-    <row r="106" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="106" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A106" s="1">
         <v>31291</v>
       </c>
@@ -4245,7 +4059,7 @@
       </c>
       <c r="I106" s="7"/>
     </row>
-    <row r="107" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="107" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A107" s="1">
         <v>31321</v>
       </c>
@@ -4272,7 +4086,7 @@
       </c>
       <c r="I107" s="7"/>
     </row>
-    <row r="108" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="108" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A108" s="1">
         <v>31352</v>
       </c>
@@ -4299,7 +4113,7 @@
       </c>
       <c r="I108" s="7"/>
     </row>
-    <row r="109" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="109" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A109" s="1">
         <v>31382</v>
       </c>
@@ -4326,7 +4140,7 @@
       </c>
       <c r="I109" s="7"/>
     </row>
-    <row r="110" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="110" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A110" s="1">
         <v>31413</v>
       </c>
@@ -4353,7 +4167,7 @@
       </c>
       <c r="I110" s="7"/>
     </row>
-    <row r="111" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="111" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A111" s="1">
         <v>31444</v>
       </c>
@@ -4380,7 +4194,7 @@
       </c>
       <c r="I111" s="7"/>
     </row>
-    <row r="112" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="112" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A112" s="1">
         <v>31472</v>
       </c>
@@ -4407,7 +4221,7 @@
       </c>
       <c r="I112" s="7"/>
     </row>
-    <row r="113" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="113" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A113" s="1">
         <v>31503</v>
       </c>
@@ -4434,7 +4248,7 @@
       </c>
       <c r="I113" s="7"/>
     </row>
-    <row r="114" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="114" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A114" s="1">
         <v>31533</v>
       </c>
@@ -4461,7 +4275,7 @@
       </c>
       <c r="I114" s="7"/>
     </row>
-    <row r="115" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="115" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A115" s="1">
         <v>31564</v>
       </c>
@@ -4488,7 +4302,7 @@
       </c>
       <c r="I115" s="7"/>
     </row>
-    <row r="116" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="116" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A116" s="1">
         <v>31594</v>
       </c>
@@ -4515,7 +4329,7 @@
       </c>
       <c r="I116" s="7"/>
     </row>
-    <row r="117" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="117" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A117" s="1">
         <v>31625</v>
       </c>
@@ -4542,7 +4356,7 @@
       </c>
       <c r="I117" s="7"/>
     </row>
-    <row r="118" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="118" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A118" s="1">
         <v>31656</v>
       </c>
@@ -4569,7 +4383,7 @@
       </c>
       <c r="I118" s="7"/>
     </row>
-    <row r="119" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="119" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A119" s="1">
         <v>31686</v>
       </c>
@@ -4596,7 +4410,7 @@
       </c>
       <c r="I119" s="7"/>
     </row>
-    <row r="120" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="120" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A120" s="1">
         <v>31717</v>
       </c>
@@ -4623,7 +4437,7 @@
       </c>
       <c r="I120" s="7"/>
     </row>
-    <row r="121" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="121" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A121" s="1">
         <v>31747</v>
       </c>
@@ -4650,7 +4464,7 @@
       </c>
       <c r="I121" s="7"/>
     </row>
-    <row r="122" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="122" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A122" s="1">
         <v>31778</v>
       </c>
@@ -4677,7 +4491,7 @@
       </c>
       <c r="I122" s="7"/>
     </row>
-    <row r="123" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="123" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A123" s="1">
         <v>31809</v>
       </c>
@@ -4704,7 +4518,7 @@
       </c>
       <c r="I123" s="7"/>
     </row>
-    <row r="124" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="124" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A124" s="1">
         <v>31837</v>
       </c>
@@ -4731,7 +4545,7 @@
       </c>
       <c r="I124" s="7"/>
     </row>
-    <row r="125" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="125" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A125" s="1">
         <v>31868</v>
       </c>
@@ -4758,7 +4572,7 @@
       </c>
       <c r="I125" s="7"/>
     </row>
-    <row r="126" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="126" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A126" s="1">
         <v>31898</v>
       </c>
@@ -4785,7 +4599,7 @@
       </c>
       <c r="I126" s="7"/>
     </row>
-    <row r="127" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="127" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A127" s="1">
         <v>31929</v>
       </c>
@@ -4812,7 +4626,7 @@
       </c>
       <c r="I127" s="7"/>
     </row>
-    <row r="128" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="128" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A128" s="1">
         <v>31959</v>
       </c>
@@ -4839,7 +4653,7 @@
       </c>
       <c r="I128" s="7"/>
     </row>
-    <row r="129" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="129" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A129" s="1">
         <v>31990</v>
       </c>
@@ -4866,7 +4680,7 @@
       </c>
       <c r="I129" s="7"/>
     </row>
-    <row r="130" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="130" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A130" s="1">
         <v>32021</v>
       </c>
@@ -4893,7 +4707,7 @@
       </c>
       <c r="I130" s="7"/>
     </row>
-    <row r="131" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="131" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A131" s="1">
         <v>32051</v>
       </c>
@@ -4920,7 +4734,7 @@
       </c>
       <c r="I131" s="7"/>
     </row>
-    <row r="132" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="132" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A132" s="1">
         <v>32082</v>
       </c>
@@ -4947,7 +4761,7 @@
       </c>
       <c r="I132" s="7"/>
     </row>
-    <row r="133" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="133" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A133" s="1">
         <v>32112</v>
       </c>
@@ -4974,7 +4788,7 @@
       </c>
       <c r="I133" s="7"/>
     </row>
-    <row r="134" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="134" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A134" s="1">
         <v>32143</v>
       </c>
@@ -5001,7 +4815,7 @@
       </c>
       <c r="I134" s="7"/>
     </row>
-    <row r="135" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="135" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A135" s="1">
         <v>32174</v>
       </c>
@@ -5028,7 +4842,7 @@
       </c>
       <c r="I135" s="7"/>
     </row>
-    <row r="136" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="136" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A136" s="1">
         <v>32203</v>
       </c>
@@ -5055,7 +4869,7 @@
       </c>
       <c r="I136" s="7"/>
     </row>
-    <row r="137" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="137" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A137" s="1">
         <v>32234</v>
       </c>
@@ -5082,7 +4896,7 @@
       </c>
       <c r="I137" s="7"/>
     </row>
-    <row r="138" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="138" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A138" s="1">
         <v>32264</v>
       </c>
@@ -5109,7 +4923,7 @@
       </c>
       <c r="I138" s="7"/>
     </row>
-    <row r="139" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="139" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A139" s="1">
         <v>32295</v>
       </c>
@@ -5136,7 +4950,7 @@
       </c>
       <c r="I139" s="7"/>
     </row>
-    <row r="140" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="140" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A140" s="1">
         <v>32325</v>
       </c>
@@ -5163,7 +4977,7 @@
       </c>
       <c r="I140" s="7"/>
     </row>
-    <row r="141" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="141" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A141" s="1">
         <v>32356</v>
       </c>
@@ -5190,7 +5004,7 @@
       </c>
       <c r="I141" s="7"/>
     </row>
-    <row r="142" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="142" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A142" s="1">
         <v>32387</v>
       </c>
@@ -5217,7 +5031,7 @@
       </c>
       <c r="I142" s="7"/>
     </row>
-    <row r="143" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="143" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A143" s="1">
         <v>32417</v>
       </c>
@@ -5244,7 +5058,7 @@
       </c>
       <c r="I143" s="7"/>
     </row>
-    <row r="144" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="144" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A144" s="1">
         <v>32448</v>
       </c>
@@ -5271,7 +5085,7 @@
       </c>
       <c r="I144" s="7"/>
     </row>
-    <row r="145" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="145" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A145" s="1">
         <v>32478</v>
       </c>
@@ -5298,7 +5112,7 @@
       </c>
       <c r="I145" s="7"/>
     </row>
-    <row r="146" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="146" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A146" s="1">
         <v>32509</v>
       </c>
@@ -5325,7 +5139,7 @@
       </c>
       <c r="I146" s="7"/>
     </row>
-    <row r="147" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="147" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A147" s="1">
         <v>32540</v>
       </c>
@@ -5352,7 +5166,7 @@
       </c>
       <c r="I147" s="7"/>
     </row>
-    <row r="148" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="148" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A148" s="1">
         <v>32568</v>
       </c>
@@ -5379,7 +5193,7 @@
       </c>
       <c r="I148" s="7"/>
     </row>
-    <row r="149" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="149" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A149" s="1">
         <v>32599</v>
       </c>
@@ -5406,7 +5220,7 @@
       </c>
       <c r="I149" s="7"/>
     </row>
-    <row r="150" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="150" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A150" s="1">
         <v>32629</v>
       </c>
@@ -5433,7 +5247,7 @@
       </c>
       <c r="I150" s="7"/>
     </row>
-    <row r="151" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="151" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A151" s="1">
         <v>32660</v>
       </c>
@@ -5460,7 +5274,7 @@
       </c>
       <c r="I151" s="7"/>
     </row>
-    <row r="152" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="152" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A152" s="1">
         <v>32690</v>
       </c>
@@ -5487,7 +5301,7 @@
       </c>
       <c r="I152" s="7"/>
     </row>
-    <row r="153" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="153" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A153" s="1">
         <v>32721</v>
       </c>
@@ -5514,7 +5328,7 @@
       </c>
       <c r="I153" s="7"/>
     </row>
-    <row r="154" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="154" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A154" s="1">
         <v>32752</v>
       </c>
@@ -5541,7 +5355,7 @@
       </c>
       <c r="I154" s="7"/>
     </row>
-    <row r="155" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="155" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A155" s="1">
         <v>32782</v>
       </c>
@@ -5568,7 +5382,7 @@
       </c>
       <c r="I155" s="7"/>
     </row>
-    <row r="156" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="156" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A156" s="1">
         <v>32813</v>
       </c>
@@ -5595,7 +5409,7 @@
       </c>
       <c r="I156" s="7"/>
     </row>
-    <row r="157" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="157" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A157" s="1">
         <v>32843</v>
       </c>
@@ -5622,7 +5436,7 @@
       </c>
       <c r="I157" s="7"/>
     </row>
-    <row r="158" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="158" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A158" s="1">
         <v>32874</v>
       </c>
@@ -5649,7 +5463,7 @@
       </c>
       <c r="I158" s="7"/>
     </row>
-    <row r="159" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="159" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A159" s="1">
         <v>32905</v>
       </c>
@@ -5676,7 +5490,7 @@
       </c>
       <c r="I159" s="7"/>
     </row>
-    <row r="160" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="160" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A160" s="1">
         <v>32933</v>
       </c>
@@ -5703,7 +5517,7 @@
       </c>
       <c r="I160" s="7"/>
     </row>
-    <row r="161" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="161" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A161" s="1">
         <v>32964</v>
       </c>
@@ -5730,7 +5544,7 @@
       </c>
       <c r="I161" s="7"/>
     </row>
-    <row r="162" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="162" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A162" s="1">
         <v>32994</v>
       </c>
@@ -5757,7 +5571,7 @@
       </c>
       <c r="I162" s="7"/>
     </row>
-    <row r="163" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="163" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A163" s="1">
         <v>33025</v>
       </c>
@@ -5784,7 +5598,7 @@
       </c>
       <c r="I163" s="7"/>
     </row>
-    <row r="164" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="164" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A164" s="1">
         <v>33055</v>
       </c>
@@ -5811,7 +5625,7 @@
       </c>
       <c r="I164" s="7"/>
     </row>
-    <row r="165" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="165" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A165" s="1">
         <v>33086</v>
       </c>
@@ -5838,7 +5652,7 @@
       </c>
       <c r="I165" s="7"/>
     </row>
-    <row r="166" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="166" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A166" s="1">
         <v>33117</v>
       </c>
@@ -5865,7 +5679,7 @@
       </c>
       <c r="I166" s="7"/>
     </row>
-    <row r="167" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="167" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A167" s="1">
         <v>33147</v>
       </c>
@@ -5892,7 +5706,7 @@
       </c>
       <c r="I167" s="7"/>
     </row>
-    <row r="168" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="168" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A168" s="1">
         <v>33178</v>
       </c>
@@ -5919,7 +5733,7 @@
       </c>
       <c r="I168" s="7"/>
     </row>
-    <row r="169" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="169" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A169" s="1">
         <v>33208</v>
       </c>
@@ -5946,7 +5760,7 @@
       </c>
       <c r="I169" s="7"/>
     </row>
-    <row r="170" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="170" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A170" s="1">
         <v>33239</v>
       </c>
@@ -5973,7 +5787,7 @@
       </c>
       <c r="I170" s="7"/>
     </row>
-    <row r="171" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="171" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A171" s="1">
         <v>33270</v>
       </c>
@@ -6000,7 +5814,7 @@
       </c>
       <c r="I171" s="7"/>
     </row>
-    <row r="172" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="172" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A172" s="1">
         <v>33298</v>
       </c>
@@ -6027,7 +5841,7 @@
       </c>
       <c r="I172" s="7"/>
     </row>
-    <row r="173" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="173" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A173" s="1">
         <v>33329</v>
       </c>
@@ -6054,7 +5868,7 @@
       </c>
       <c r="I173" s="7"/>
     </row>
-    <row r="174" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="174" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A174" s="1">
         <v>33359</v>
       </c>
@@ -6081,7 +5895,7 @@
       </c>
       <c r="I174" s="7"/>
     </row>
-    <row r="175" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="175" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A175" s="1">
         <v>33390</v>
       </c>
@@ -6108,7 +5922,7 @@
       </c>
       <c r="I175" s="7"/>
     </row>
-    <row r="176" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="176" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A176" s="1">
         <v>33420</v>
       </c>
@@ -6135,7 +5949,7 @@
       </c>
       <c r="I176" s="7"/>
     </row>
-    <row r="177" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="177" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A177" s="1">
         <v>33451</v>
       </c>
@@ -6162,7 +5976,7 @@
       </c>
       <c r="I177" s="7"/>
     </row>
-    <row r="178" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="178" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A178" s="1">
         <v>33482</v>
       </c>
@@ -6189,7 +6003,7 @@
       </c>
       <c r="I178" s="7"/>
     </row>
-    <row r="179" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="179" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A179" s="1">
         <v>33512</v>
       </c>
@@ -6216,7 +6030,7 @@
       </c>
       <c r="I179" s="7"/>
     </row>
-    <row r="180" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="180" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A180" s="1">
         <v>33543</v>
       </c>
@@ -6243,7 +6057,7 @@
       </c>
       <c r="I180" s="7"/>
     </row>
-    <row r="181" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="181" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A181" s="1">
         <v>33573</v>
       </c>
@@ -6270,7 +6084,7 @@
       </c>
       <c r="I181" s="7"/>
     </row>
-    <row r="182" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="182" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A182" s="1">
         <v>33604</v>
       </c>
@@ -6297,7 +6111,7 @@
       </c>
       <c r="I182" s="7"/>
     </row>
-    <row r="183" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="183" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A183" s="1">
         <v>33635</v>
       </c>
@@ -6324,7 +6138,7 @@
       </c>
       <c r="I183" s="7"/>
     </row>
-    <row r="184" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="184" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A184" s="1">
         <v>33664</v>
       </c>
@@ -6351,7 +6165,7 @@
       </c>
       <c r="I184" s="7"/>
     </row>
-    <row r="185" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="185" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A185" s="1">
         <v>33695</v>
       </c>
@@ -6378,7 +6192,7 @@
       </c>
       <c r="I185" s="7"/>
     </row>
-    <row r="186" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="186" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A186" s="1">
         <v>33725</v>
       </c>
@@ -6405,7 +6219,7 @@
       </c>
       <c r="I186" s="7"/>
     </row>
-    <row r="187" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="187" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A187" s="1">
         <v>33756</v>
       </c>
@@ -6432,7 +6246,7 @@
       </c>
       <c r="I187" s="7"/>
     </row>
-    <row r="188" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="188" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A188" s="1">
         <v>33786</v>
       </c>
@@ -6459,7 +6273,7 @@
       </c>
       <c r="I188" s="7"/>
     </row>
-    <row r="189" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="189" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A189" s="1">
         <v>33817</v>
       </c>
@@ -6486,7 +6300,7 @@
       </c>
       <c r="I189" s="7"/>
     </row>
-    <row r="190" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="190" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A190" s="1">
         <v>33848</v>
       </c>
@@ -6513,7 +6327,7 @@
       </c>
       <c r="I190" s="7"/>
     </row>
-    <row r="191" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="191" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A191" s="1">
         <v>33878</v>
       </c>
@@ -6540,7 +6354,7 @@
       </c>
       <c r="I191" s="7"/>
     </row>
-    <row r="192" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="192" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A192" s="1">
         <v>33909</v>
       </c>
@@ -6567,7 +6381,7 @@
       </c>
       <c r="I192" s="7"/>
     </row>
-    <row r="193" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="193" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A193" s="1">
         <v>33939</v>
       </c>
@@ -6594,7 +6408,7 @@
       </c>
       <c r="I193" s="7"/>
     </row>
-    <row r="194" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="194" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A194" s="1">
         <v>33970</v>
       </c>
@@ -6621,7 +6435,7 @@
       </c>
       <c r="I194" s="7"/>
     </row>
-    <row r="195" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="195" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A195" s="1">
         <v>34001</v>
       </c>
@@ -6648,7 +6462,7 @@
       </c>
       <c r="I195" s="7"/>
     </row>
-    <row r="196" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="196" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A196" s="1">
         <v>34029</v>
       </c>
@@ -6675,7 +6489,7 @@
       </c>
       <c r="I196" s="7"/>
     </row>
-    <row r="197" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="197" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A197" s="1">
         <v>34060</v>
       </c>
@@ -6702,7 +6516,7 @@
       </c>
       <c r="I197" s="7"/>
     </row>
-    <row r="198" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="198" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A198" s="1">
         <v>34090</v>
       </c>
@@ -6729,7 +6543,7 @@
       </c>
       <c r="I198" s="7"/>
     </row>
-    <row r="199" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="199" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A199" s="1">
         <v>34121</v>
       </c>
@@ -6756,7 +6570,7 @@
       </c>
       <c r="I199" s="7"/>
     </row>
-    <row r="200" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="200" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A200" s="1">
         <v>34151</v>
       </c>
@@ -6783,7 +6597,7 @@
       </c>
       <c r="I200" s="7"/>
     </row>
-    <row r="201" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="201" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A201" s="1">
         <v>34182</v>
       </c>
@@ -6810,7 +6624,7 @@
       </c>
       <c r="I201" s="7"/>
     </row>
-    <row r="202" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="202" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A202" s="1">
         <v>34213</v>
       </c>
@@ -6837,7 +6651,7 @@
       </c>
       <c r="I202" s="7"/>
     </row>
-    <row r="203" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="203" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A203" s="1">
         <v>34243</v>
       </c>
@@ -6864,7 +6678,7 @@
       </c>
       <c r="I203" s="7"/>
     </row>
-    <row r="204" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="204" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A204" s="1">
         <v>34274</v>
       </c>
@@ -6891,7 +6705,7 @@
       </c>
       <c r="I204" s="7"/>
     </row>
-    <row r="205" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="205" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A205" s="1">
         <v>34304</v>
       </c>
@@ -6918,7 +6732,7 @@
       </c>
       <c r="I205" s="7"/>
     </row>
-    <row r="206" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="206" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A206" s="1">
         <v>34335</v>
       </c>
@@ -6945,7 +6759,7 @@
       </c>
       <c r="I206" s="7"/>
     </row>
-    <row r="207" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="207" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A207" s="1">
         <v>34366</v>
       </c>
@@ -6972,7 +6786,7 @@
       </c>
       <c r="I207" s="7"/>
     </row>
-    <row r="208" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="208" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A208" s="1">
         <v>34394</v>
       </c>
@@ -6999,7 +6813,7 @@
       </c>
       <c r="I208" s="7"/>
     </row>
-    <row r="209" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="209" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A209" s="1">
         <v>34425</v>
       </c>
@@ -7026,7 +6840,7 @@
       </c>
       <c r="I209" s="7"/>
     </row>
-    <row r="210" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="210" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A210" s="1">
         <v>34455</v>
       </c>
@@ -7053,7 +6867,7 @@
       </c>
       <c r="I210" s="7"/>
     </row>
-    <row r="211" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="211" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A211" s="1">
         <v>34486</v>
       </c>
@@ -7080,7 +6894,7 @@
       </c>
       <c r="I211" s="7"/>
     </row>
-    <row r="212" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="212" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A212" s="1">
         <v>34516</v>
       </c>
@@ -7107,7 +6921,7 @@
       </c>
       <c r="I212" s="7"/>
     </row>
-    <row r="213" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="213" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A213" s="1">
         <v>34547</v>
       </c>
@@ -7134,7 +6948,7 @@
       </c>
       <c r="I213" s="7"/>
     </row>
-    <row r="214" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="214" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A214" s="1">
         <v>34578</v>
       </c>
@@ -7161,7 +6975,7 @@
       </c>
       <c r="I214" s="7"/>
     </row>
-    <row r="215" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="215" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A215" s="1">
         <v>34608</v>
       </c>
@@ -7188,7 +7002,7 @@
       </c>
       <c r="I215" s="7"/>
     </row>
-    <row r="216" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="216" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A216" s="1">
         <v>34639</v>
       </c>
@@ -7215,7 +7029,7 @@
       </c>
       <c r="I216" s="7"/>
     </row>
-    <row r="217" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="217" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A217" s="1">
         <v>34669</v>
       </c>
@@ -7242,7 +7056,7 @@
       </c>
       <c r="I217" s="7"/>
     </row>
-    <row r="218" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="218" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A218" s="1">
         <v>34700</v>
       </c>
@@ -7269,7 +7083,7 @@
       </c>
       <c r="I218" s="7"/>
     </row>
-    <row r="219" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="219" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A219" s="1">
         <v>34731</v>
       </c>
@@ -7296,7 +7110,7 @@
       </c>
       <c r="I219" s="7"/>
     </row>
-    <row r="220" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="220" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A220" s="1">
         <v>34759</v>
       </c>
@@ -7323,7 +7137,7 @@
       </c>
       <c r="I220" s="7"/>
     </row>
-    <row r="221" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="221" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A221" s="1">
         <v>34790</v>
       </c>
@@ -7350,7 +7164,7 @@
       </c>
       <c r="I221" s="7"/>
     </row>
-    <row r="222" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="222" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A222" s="1">
         <v>34820</v>
       </c>
@@ -7377,7 +7191,7 @@
       </c>
       <c r="I222" s="7"/>
     </row>
-    <row r="223" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="223" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A223" s="1">
         <v>34851</v>
       </c>
@@ -7404,7 +7218,7 @@
       </c>
       <c r="I223" s="7"/>
     </row>
-    <row r="224" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="224" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A224" s="1">
         <v>34881</v>
       </c>
@@ -7431,7 +7245,7 @@
       </c>
       <c r="I224" s="7"/>
     </row>
-    <row r="225" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="225" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A225" s="1">
         <v>34912</v>
       </c>
@@ -7458,7 +7272,7 @@
       </c>
       <c r="I225" s="7"/>
     </row>
-    <row r="226" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="226" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A226" s="1">
         <v>34943</v>
       </c>
@@ -7485,7 +7299,7 @@
       </c>
       <c r="I226" s="7"/>
     </row>
-    <row r="227" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="227" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A227" s="1">
         <v>34973</v>
       </c>
@@ -7512,7 +7326,7 @@
       </c>
       <c r="I227" s="7"/>
     </row>
-    <row r="228" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="228" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A228" s="1">
         <v>35004</v>
       </c>
@@ -7539,7 +7353,7 @@
       </c>
       <c r="I228" s="7"/>
     </row>
-    <row r="229" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="229" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A229" s="1">
         <v>35034</v>
       </c>
@@ -7566,7 +7380,7 @@
       </c>
       <c r="I229" s="7"/>
     </row>
-    <row r="230" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="230" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A230" s="1">
         <v>35065</v>
       </c>
@@ -7593,7 +7407,7 @@
       </c>
       <c r="I230" s="7"/>
     </row>
-    <row r="231" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="231" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A231" s="1">
         <v>35096</v>
       </c>
@@ -7620,7 +7434,7 @@
       </c>
       <c r="I231" s="7"/>
     </row>
-    <row r="232" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="232" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A232" s="1">
         <v>35125</v>
       </c>
@@ -7647,7 +7461,7 @@
       </c>
       <c r="I232" s="7"/>
     </row>
-    <row r="233" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="233" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A233" s="1">
         <v>35156</v>
       </c>
@@ -7674,7 +7488,7 @@
       </c>
       <c r="I233" s="7"/>
     </row>
-    <row r="234" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="234" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A234" s="1">
         <v>35186</v>
       </c>
@@ -7701,7 +7515,7 @@
       </c>
       <c r="I234" s="7"/>
     </row>
-    <row r="235" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="235" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A235" s="1">
         <v>35217</v>
       </c>
@@ -7728,7 +7542,7 @@
       </c>
       <c r="I235" s="7"/>
     </row>
-    <row r="236" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="236" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A236" s="1">
         <v>35247</v>
       </c>
@@ -7755,7 +7569,7 @@
       </c>
       <c r="I236" s="7"/>
     </row>
-    <row r="237" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="237" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A237" s="1">
         <v>35278</v>
       </c>
@@ -7782,7 +7596,7 @@
       </c>
       <c r="I237" s="7"/>
     </row>
-    <row r="238" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="238" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A238" s="1">
         <v>35309</v>
       </c>
@@ -7809,7 +7623,7 @@
       </c>
       <c r="I238" s="7"/>
     </row>
-    <row r="239" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="239" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A239" s="1">
         <v>35339</v>
       </c>
@@ -7836,7 +7650,7 @@
       </c>
       <c r="I239" s="7"/>
     </row>
-    <row r="240" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="240" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A240" s="1">
         <v>35370</v>
       </c>
@@ -7863,7 +7677,7 @@
       </c>
       <c r="I240" s="7"/>
     </row>
-    <row r="241" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="241" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A241" s="1">
         <v>35400</v>
       </c>
@@ -7890,7 +7704,7 @@
       </c>
       <c r="I241" s="7"/>
     </row>
-    <row r="242" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="242" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A242" s="1">
         <v>35431</v>
       </c>
@@ -7917,7 +7731,7 @@
       </c>
       <c r="I242" s="7"/>
     </row>
-    <row r="243" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="243" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A243" s="1">
         <v>35462</v>
       </c>
@@ -7944,7 +7758,7 @@
       </c>
       <c r="I243" s="7"/>
     </row>
-    <row r="244" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="244" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A244" s="1">
         <v>35490</v>
       </c>
@@ -7971,7 +7785,7 @@
       </c>
       <c r="I244" s="7"/>
     </row>
-    <row r="245" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="245" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A245" s="1">
         <v>35521</v>
       </c>
@@ -7998,7 +7812,7 @@
       </c>
       <c r="I245" s="7"/>
     </row>
-    <row r="246" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="246" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A246" s="1">
         <v>35551</v>
       </c>
@@ -8025,7 +7839,7 @@
       </c>
       <c r="I246" s="7"/>
     </row>
-    <row r="247" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="247" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A247" s="1">
         <v>35582</v>
       </c>
@@ -8052,7 +7866,7 @@
       </c>
       <c r="I247" s="7"/>
     </row>
-    <row r="248" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="248" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A248" s="1">
         <v>35612</v>
       </c>
@@ -8079,7 +7893,7 @@
       </c>
       <c r="I248" s="7"/>
     </row>
-    <row r="249" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="249" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A249" s="1">
         <v>35643</v>
       </c>
@@ -8106,7 +7920,7 @@
       </c>
       <c r="I249" s="7"/>
     </row>
-    <row r="250" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="250" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A250" s="1">
         <v>35674</v>
       </c>
@@ -8133,7 +7947,7 @@
       </c>
       <c r="I250" s="7"/>
     </row>
-    <row r="251" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="251" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A251" s="1">
         <v>35704</v>
       </c>
@@ -8160,7 +7974,7 @@
       </c>
       <c r="I251" s="7"/>
     </row>
-    <row r="252" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="252" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A252" s="1">
         <v>35735</v>
       </c>
@@ -8187,7 +8001,7 @@
       </c>
       <c r="I252" s="7"/>
     </row>
-    <row r="253" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="253" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A253" s="1">
         <v>35765</v>
       </c>
@@ -8214,7 +8028,7 @@
       </c>
       <c r="I253" s="7"/>
     </row>
-    <row r="254" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="254" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A254" s="1">
         <v>35796</v>
       </c>
@@ -8241,7 +8055,7 @@
       </c>
       <c r="I254" s="7"/>
     </row>
-    <row r="255" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="255" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A255" s="1">
         <v>35827</v>
       </c>
@@ -8268,7 +8082,7 @@
       </c>
       <c r="I255" s="7"/>
     </row>
-    <row r="256" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="256" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A256" s="1">
         <v>35855</v>
       </c>
@@ -8295,7 +8109,7 @@
       </c>
       <c r="I256" s="7"/>
     </row>
-    <row r="257" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="257" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A257" s="1">
         <v>35886</v>
       </c>
@@ -8322,7 +8136,7 @@
       </c>
       <c r="I257" s="7"/>
     </row>
-    <row r="258" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="258" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A258" s="1">
         <v>35916</v>
       </c>
@@ -8349,7 +8163,7 @@
       </c>
       <c r="I258" s="7"/>
     </row>
-    <row r="259" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="259" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A259" s="1">
         <v>35947</v>
       </c>
@@ -8376,7 +8190,7 @@
       </c>
       <c r="I259" s="7"/>
     </row>
-    <row r="260" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="260" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A260" s="1">
         <v>35977</v>
       </c>
@@ -8403,7 +8217,7 @@
       </c>
       <c r="I260" s="7"/>
     </row>
-    <row r="261" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="261" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A261" s="1">
         <v>36008</v>
       </c>
@@ -8430,7 +8244,7 @@
       </c>
       <c r="I261" s="7"/>
     </row>
-    <row r="262" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="262" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A262" s="1">
         <v>36039</v>
       </c>
@@ -8457,7 +8271,7 @@
       </c>
       <c r="I262" s="7"/>
     </row>
-    <row r="263" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="263" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A263" s="1">
         <v>36069</v>
       </c>
@@ -8484,7 +8298,7 @@
       </c>
       <c r="I263" s="7"/>
     </row>
-    <row r="264" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="264" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A264" s="1">
         <v>36100</v>
       </c>
@@ -8511,7 +8325,7 @@
       </c>
       <c r="I264" s="7"/>
     </row>
-    <row r="265" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="265" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A265" s="1">
         <v>36130</v>
       </c>
@@ -8538,7 +8352,7 @@
       </c>
       <c r="I265" s="7"/>
     </row>
-    <row r="266" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="266" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A266" s="1">
         <v>36161</v>
       </c>
@@ -8565,7 +8379,7 @@
       </c>
       <c r="I266" s="7"/>
     </row>
-    <row r="267" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="267" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A267" s="1">
         <v>36192</v>
       </c>
@@ -8592,7 +8406,7 @@
       </c>
       <c r="I267" s="7"/>
     </row>
-    <row r="268" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="268" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A268" s="1">
         <v>36220</v>
       </c>
@@ -8619,7 +8433,7 @@
       </c>
       <c r="I268" s="7"/>
     </row>
-    <row r="269" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="269" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A269" s="1">
         <v>36251</v>
       </c>
@@ -8646,7 +8460,7 @@
       </c>
       <c r="I269" s="7"/>
     </row>
-    <row r="270" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="270" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A270" s="1">
         <v>36281</v>
       </c>
@@ -8673,7 +8487,7 @@
       </c>
       <c r="I270" s="7"/>
     </row>
-    <row r="271" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="271" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A271" s="1">
         <v>36312</v>
       </c>
@@ -8700,7 +8514,7 @@
       </c>
       <c r="I271" s="7"/>
     </row>
-    <row r="272" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="272" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A272" s="1">
         <v>36342</v>
       </c>
@@ -8727,7 +8541,7 @@
       </c>
       <c r="I272" s="7"/>
     </row>
-    <row r="273" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="273" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A273" s="1">
         <v>36373</v>
       </c>
@@ -8754,7 +8568,7 @@
       </c>
       <c r="I273" s="7"/>
     </row>
-    <row r="274" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="274" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A274" s="1">
         <v>36404</v>
       </c>
@@ -8781,7 +8595,7 @@
       </c>
       <c r="I274" s="7"/>
     </row>
-    <row r="275" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="275" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A275" s="1">
         <v>36434</v>
       </c>
@@ -8808,7 +8622,7 @@
       </c>
       <c r="I275" s="7"/>
     </row>
-    <row r="276" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="276" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A276" s="1">
         <v>36465</v>
       </c>
@@ -8835,7 +8649,7 @@
       </c>
       <c r="I276" s="7"/>
     </row>
-    <row r="277" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="277" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A277" s="1">
         <v>36495</v>
       </c>
@@ -8862,7 +8676,7 @@
       </c>
       <c r="I277" s="7"/>
     </row>
-    <row r="278" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="278" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A278" s="1">
         <v>36526</v>
       </c>
@@ -8889,7 +8703,7 @@
       </c>
       <c r="I278" s="7"/>
     </row>
-    <row r="279" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="279" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A279" s="1">
         <v>36557</v>
       </c>
@@ -8916,7 +8730,7 @@
       </c>
       <c r="I279" s="7"/>
     </row>
-    <row r="280" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="280" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A280" s="1">
         <v>36586</v>
       </c>
@@ -8943,7 +8757,7 @@
       </c>
       <c r="I280" s="7"/>
     </row>
-    <row r="281" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="281" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A281" s="1">
         <v>36617</v>
       </c>
@@ -8970,7 +8784,7 @@
       </c>
       <c r="I281" s="7"/>
     </row>
-    <row r="282" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="282" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A282" s="1">
         <v>36647</v>
       </c>
@@ -8997,7 +8811,7 @@
       </c>
       <c r="I282" s="7"/>
     </row>
-    <row r="283" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="283" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A283" s="1">
         <v>36678</v>
       </c>
@@ -9024,7 +8838,7 @@
       </c>
       <c r="I283" s="7"/>
     </row>
-    <row r="284" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="284" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A284" s="1">
         <v>36708</v>
       </c>
@@ -9051,7 +8865,7 @@
       </c>
       <c r="I284" s="7"/>
     </row>
-    <row r="285" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="285" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A285" s="1">
         <v>36739</v>
       </c>
@@ -9078,7 +8892,7 @@
       </c>
       <c r="I285" s="7"/>
     </row>
-    <row r="286" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="286" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A286" s="1">
         <v>36770</v>
       </c>
@@ -9105,7 +8919,7 @@
       </c>
       <c r="I286" s="7"/>
     </row>
-    <row r="287" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="287" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A287" s="1">
         <v>36800</v>
       </c>
@@ -9132,7 +8946,7 @@
       </c>
       <c r="I287" s="7"/>
     </row>
-    <row r="288" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="288" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A288" s="1">
         <v>36831</v>
       </c>
@@ -9159,7 +8973,7 @@
       </c>
       <c r="I288" s="7"/>
     </row>
-    <row r="289" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="289" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A289" s="1">
         <v>36861</v>
       </c>
@@ -9186,7 +9000,7 @@
       </c>
       <c r="I289" s="7"/>
     </row>
-    <row r="290" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="290" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A290" s="1">
         <v>36892</v>
       </c>
@@ -9213,7 +9027,7 @@
       </c>
       <c r="I290" s="7"/>
     </row>
-    <row r="291" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="291" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A291" s="1">
         <v>36923</v>
       </c>
@@ -9240,7 +9054,7 @@
       </c>
       <c r="I291" s="7"/>
     </row>
-    <row r="292" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="292" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A292" s="1">
         <v>36951</v>
       </c>
@@ -9267,7 +9081,7 @@
       </c>
       <c r="I292" s="7"/>
     </row>
-    <row r="293" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="293" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A293" s="1">
         <v>36982</v>
       </c>
@@ -9294,7 +9108,7 @@
       </c>
       <c r="I293" s="7"/>
     </row>
-    <row r="294" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="294" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A294" s="1">
         <v>37012</v>
       </c>
@@ -9321,7 +9135,7 @@
       </c>
       <c r="I294" s="7"/>
     </row>
-    <row r="295" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="295" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A295" s="1">
         <v>37043</v>
       </c>
@@ -9348,7 +9162,7 @@
       </c>
       <c r="I295" s="7"/>
     </row>
-    <row r="296" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="296" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A296" s="1">
         <v>37073</v>
       </c>
@@ -9375,7 +9189,7 @@
       </c>
       <c r="I296" s="7"/>
     </row>
-    <row r="297" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="297" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A297" s="1">
         <v>37104</v>
       </c>
@@ -9402,7 +9216,7 @@
       </c>
       <c r="I297" s="7"/>
     </row>
-    <row r="298" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="298" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A298" s="1">
         <v>37135</v>
       </c>
@@ -9429,7 +9243,7 @@
       </c>
       <c r="I298" s="7"/>
     </row>
-    <row r="299" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="299" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A299" s="1">
         <v>37165</v>
       </c>
@@ -9456,7 +9270,7 @@
       </c>
       <c r="I299" s="7"/>
     </row>
-    <row r="300" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="300" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A300" s="1">
         <v>37196</v>
       </c>
@@ -9483,7 +9297,7 @@
       </c>
       <c r="I300" s="7"/>
     </row>
-    <row r="301" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="301" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A301" s="1">
         <v>37226</v>
       </c>
@@ -9510,7 +9324,7 @@
       </c>
       <c r="I301" s="7"/>
     </row>
-    <row r="302" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="302" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A302" s="1">
         <v>37257</v>
       </c>
@@ -9537,7 +9351,7 @@
       </c>
       <c r="I302" s="7"/>
     </row>
-    <row r="303" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="303" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A303" s="1">
         <v>37288</v>
       </c>
@@ -9564,7 +9378,7 @@
       </c>
       <c r="I303" s="7"/>
     </row>
-    <row r="304" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="304" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A304" s="1">
         <v>37316</v>
       </c>
@@ -9591,7 +9405,7 @@
       </c>
       <c r="I304" s="7"/>
     </row>
-    <row r="305" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="305" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A305" s="1">
         <v>37347</v>
       </c>
@@ -9618,7 +9432,7 @@
       </c>
       <c r="I305" s="7"/>
     </row>
-    <row r="306" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="306" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A306" s="1">
         <v>37377</v>
       </c>
@@ -9645,7 +9459,7 @@
       </c>
       <c r="I306" s="7"/>
     </row>
-    <row r="307" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="307" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A307" s="1">
         <v>37408</v>
       </c>
@@ -9672,7 +9486,7 @@
       </c>
       <c r="I307" s="7"/>
     </row>
-    <row r="308" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="308" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A308" s="1">
         <v>37438</v>
       </c>
@@ -9699,7 +9513,7 @@
       </c>
       <c r="I308" s="7"/>
     </row>
-    <row r="309" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="309" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A309" s="1">
         <v>37469</v>
       </c>
@@ -9726,7 +9540,7 @@
       </c>
       <c r="I309" s="7"/>
     </row>
-    <row r="310" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="310" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A310" s="1">
         <v>37500</v>
       </c>
@@ -9753,7 +9567,7 @@
       </c>
       <c r="I310" s="7"/>
     </row>
-    <row r="311" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="311" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A311" s="1">
         <v>37530</v>
       </c>
@@ -9780,7 +9594,7 @@
       </c>
       <c r="I311" s="7"/>
     </row>
-    <row r="312" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="312" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A312" s="1">
         <v>37561</v>
       </c>
@@ -9807,7 +9621,7 @@
       </c>
       <c r="I312" s="7"/>
     </row>
-    <row r="313" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="313" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A313" s="1">
         <v>37591</v>
       </c>
@@ -9834,7 +9648,7 @@
       </c>
       <c r="I313" s="7"/>
     </row>
-    <row r="314" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="314" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A314" s="1">
         <v>37622</v>
       </c>
@@ -9861,7 +9675,7 @@
       </c>
       <c r="I314" s="7"/>
     </row>
-    <row r="315" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="315" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A315" s="1">
         <v>37653</v>
       </c>
@@ -9888,7 +9702,7 @@
       </c>
       <c r="I315" s="7"/>
     </row>
-    <row r="316" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="316" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A316" s="1">
         <v>37681</v>
       </c>
@@ -9915,7 +9729,7 @@
       </c>
       <c r="I316" s="7"/>
     </row>
-    <row r="317" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="317" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A317" s="1">
         <v>37712</v>
       </c>
@@ -9942,7 +9756,7 @@
       </c>
       <c r="I317" s="7"/>
     </row>
-    <row r="318" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="318" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A318" s="1">
         <v>37742</v>
       </c>
@@ -9969,7 +9783,7 @@
       </c>
       <c r="I318" s="7"/>
     </row>
-    <row r="319" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="319" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A319" s="1">
         <v>37773</v>
       </c>
@@ -9996,7 +9810,7 @@
       </c>
       <c r="I319" s="7"/>
     </row>
-    <row r="320" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="320" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A320" s="1">
         <v>37803</v>
       </c>
@@ -10023,7 +9837,7 @@
       </c>
       <c r="I320" s="7"/>
     </row>
-    <row r="321" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="321" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A321" s="1">
         <v>37834</v>
       </c>
@@ -10050,7 +9864,7 @@
       </c>
       <c r="I321" s="7"/>
     </row>
-    <row r="322" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="322" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A322" s="1">
         <v>37865</v>
       </c>
@@ -10077,7 +9891,7 @@
       </c>
       <c r="I322" s="7"/>
     </row>
-    <row r="323" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="323" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A323" s="1">
         <v>37895</v>
       </c>
@@ -10104,7 +9918,7 @@
       </c>
       <c r="I323" s="7"/>
     </row>
-    <row r="324" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="324" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A324" s="1">
         <v>37926</v>
       </c>
@@ -10131,7 +9945,7 @@
       </c>
       <c r="I324" s="7"/>
     </row>
-    <row r="325" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="325" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A325" s="1">
         <v>37956</v>
       </c>
@@ -10158,7 +9972,7 @@
       </c>
       <c r="I325" s="7"/>
     </row>
-    <row r="326" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="326" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A326" s="1">
         <v>37987</v>
       </c>
@@ -10185,7 +9999,7 @@
       </c>
       <c r="I326" s="7"/>
     </row>
-    <row r="327" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="327" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A327" s="1">
         <v>38018</v>
       </c>
@@ -10212,7 +10026,7 @@
       </c>
       <c r="I327" s="7"/>
     </row>
-    <row r="328" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="328" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A328" s="1">
         <v>38047</v>
       </c>
@@ -10239,7 +10053,7 @@
       </c>
       <c r="I328" s="7"/>
     </row>
-    <row r="329" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="329" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A329" s="1">
         <v>38078</v>
       </c>
@@ -10266,7 +10080,7 @@
       </c>
       <c r="I329" s="7"/>
     </row>
-    <row r="330" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="330" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A330" s="1">
         <v>38108</v>
       </c>
@@ -10293,7 +10107,7 @@
       </c>
       <c r="I330" s="7"/>
     </row>
-    <row r="331" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="331" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A331" s="1">
         <v>38139</v>
       </c>
@@ -10320,7 +10134,7 @@
       </c>
       <c r="I331" s="7"/>
     </row>
-    <row r="332" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="332" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A332" s="1">
         <v>38169</v>
       </c>
@@ -10347,7 +10161,7 @@
       </c>
       <c r="I332" s="7"/>
     </row>
-    <row r="333" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="333" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A333" s="1">
         <v>38200</v>
       </c>
@@ -10374,7 +10188,7 @@
       </c>
       <c r="I333" s="7"/>
     </row>
-    <row r="334" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="334" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A334" s="1">
         <v>38231</v>
       </c>
@@ -10401,7 +10215,7 @@
       </c>
       <c r="I334" s="7"/>
     </row>
-    <row r="335" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="335" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A335" s="1">
         <v>38261</v>
       </c>
@@ -10428,7 +10242,7 @@
       </c>
       <c r="I335" s="7"/>
     </row>
-    <row r="336" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="336" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A336" s="1">
         <v>38292</v>
       </c>
@@ -10455,7 +10269,7 @@
       </c>
       <c r="I336" s="7"/>
     </row>
-    <row r="337" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="337" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A337" s="1">
         <v>38322</v>
       </c>
@@ -10482,7 +10296,7 @@
       </c>
       <c r="I337" s="7"/>
     </row>
-    <row r="338" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="338" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A338" s="1">
         <v>38353</v>
       </c>
@@ -10509,7 +10323,7 @@
       </c>
       <c r="I338" s="7"/>
     </row>
-    <row r="339" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="339" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A339" s="1">
         <v>38384</v>
       </c>
@@ -10536,7 +10350,7 @@
       </c>
       <c r="I339" s="7"/>
     </row>
-    <row r="340" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="340" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A340" s="1">
         <v>38412</v>
       </c>
@@ -10563,7 +10377,7 @@
       </c>
       <c r="I340" s="7"/>
     </row>
-    <row r="341" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="341" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A341" s="1">
         <v>38443</v>
       </c>
@@ -10590,7 +10404,7 @@
       </c>
       <c r="I341" s="7"/>
     </row>
-    <row r="342" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="342" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A342" s="1">
         <v>38473</v>
       </c>
@@ -10617,7 +10431,7 @@
       </c>
       <c r="I342" s="7"/>
     </row>
-    <row r="343" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="343" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A343" s="1">
         <v>38504</v>
       </c>
@@ -10644,7 +10458,7 @@
       </c>
       <c r="I343" s="7"/>
     </row>
-    <row r="344" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="344" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A344" s="1">
         <v>38534</v>
       </c>
@@ -10671,7 +10485,7 @@
       </c>
       <c r="I344" s="7"/>
     </row>
-    <row r="345" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="345" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A345" s="1">
         <v>38565</v>
       </c>
@@ -10698,7 +10512,7 @@
       </c>
       <c r="I345" s="7"/>
     </row>
-    <row r="346" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="346" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A346" s="1">
         <v>38596</v>
       </c>
@@ -10725,7 +10539,7 @@
       </c>
       <c r="I346" s="7"/>
     </row>
-    <row r="347" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="347" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A347" s="1">
         <v>38626</v>
       </c>
@@ -10752,7 +10566,7 @@
       </c>
       <c r="I347" s="7"/>
     </row>
-    <row r="348" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="348" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A348" s="1">
         <v>38657</v>
       </c>
@@ -10779,7 +10593,7 @@
       </c>
       <c r="I348" s="7"/>
     </row>
-    <row r="349" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="349" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A349" s="1">
         <v>38687</v>
       </c>
@@ -10806,7 +10620,7 @@
       </c>
       <c r="I349" s="7"/>
     </row>
-    <row r="350" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="350" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A350" s="1">
         <v>38718</v>
       </c>
@@ -10833,7 +10647,7 @@
       </c>
       <c r="I350" s="7"/>
     </row>
-    <row r="351" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="351" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A351" s="1">
         <v>38749</v>
       </c>
@@ -10860,7 +10674,7 @@
       </c>
       <c r="I351" s="7"/>
     </row>
-    <row r="352" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="352" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A352" s="1">
         <v>38777</v>
       </c>
@@ -10887,7 +10701,7 @@
       </c>
       <c r="I352" s="7"/>
     </row>
-    <row r="353" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="353" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A353" s="1">
         <v>38808</v>
       </c>
@@ -10914,7 +10728,7 @@
       </c>
       <c r="I353" s="7"/>
     </row>
-    <row r="354" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="354" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A354" s="1">
         <v>38838</v>
       </c>
@@ -10941,7 +10755,7 @@
       </c>
       <c r="I354" s="7"/>
     </row>
-    <row r="355" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="355" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A355" s="1">
         <v>38869</v>
       </c>
@@ -10968,7 +10782,7 @@
       </c>
       <c r="I355" s="7"/>
     </row>
-    <row r="356" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="356" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A356" s="1">
         <v>38899</v>
       </c>
@@ -10995,7 +10809,7 @@
       </c>
       <c r="I356" s="7"/>
     </row>
-    <row r="357" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="357" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A357" s="1">
         <v>38930</v>
       </c>
@@ -11022,7 +10836,7 @@
       </c>
       <c r="I357" s="7"/>
     </row>
-    <row r="358" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="358" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A358" s="1">
         <v>38961</v>
       </c>
@@ -11049,7 +10863,7 @@
       </c>
       <c r="I358" s="7"/>
     </row>
-    <row r="359" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="359" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A359" s="1">
         <v>38991</v>
       </c>
@@ -11076,7 +10890,7 @@
       </c>
       <c r="I359" s="7"/>
     </row>
-    <row r="360" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="360" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A360" s="1">
         <v>39022</v>
       </c>
@@ -11103,7 +10917,7 @@
       </c>
       <c r="I360" s="7"/>
     </row>
-    <row r="361" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="361" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A361" s="1">
         <v>39052</v>
       </c>
@@ -11130,7 +10944,7 @@
       </c>
       <c r="I361" s="7"/>
     </row>
-    <row r="362" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="362" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A362" s="1">
         <v>39083</v>
       </c>
@@ -11157,7 +10971,7 @@
       </c>
       <c r="I362" s="7"/>
     </row>
-    <row r="363" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="363" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A363" s="1">
         <v>39114</v>
       </c>
@@ -11184,7 +10998,7 @@
       </c>
       <c r="I363" s="7"/>
     </row>
-    <row r="364" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="364" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A364" s="1">
         <v>39142</v>
       </c>
@@ -11211,7 +11025,7 @@
       </c>
       <c r="I364" s="7"/>
     </row>
-    <row r="365" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="365" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A365" s="1">
         <v>39173</v>
       </c>
@@ -11238,7 +11052,7 @@
       </c>
       <c r="I365" s="7"/>
     </row>
-    <row r="366" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="366" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A366" s="1">
         <v>39203</v>
       </c>
@@ -11265,7 +11079,7 @@
       </c>
       <c r="I366" s="7"/>
     </row>
-    <row r="367" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="367" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A367" s="1">
         <v>39234</v>
       </c>
@@ -11292,7 +11106,7 @@
       </c>
       <c r="I367" s="7"/>
     </row>
-    <row r="368" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="368" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A368" s="1">
         <v>39264</v>
       </c>
@@ -11319,7 +11133,7 @@
       </c>
       <c r="I368" s="7"/>
     </row>
-    <row r="369" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="369" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A369" s="1">
         <v>39295</v>
       </c>
@@ -11346,7 +11160,7 @@
       </c>
       <c r="I369" s="7"/>
     </row>
-    <row r="370" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="370" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A370" s="1">
         <v>39326</v>
       </c>
@@ -11373,7 +11187,7 @@
       </c>
       <c r="I370" s="7"/>
     </row>
-    <row r="371" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="371" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A371" s="1">
         <v>39356</v>
       </c>
@@ -11400,7 +11214,7 @@
       </c>
       <c r="I371" s="7"/>
     </row>
-    <row r="372" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="372" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A372" s="1">
         <v>39387</v>
       </c>
@@ -11427,7 +11241,7 @@
       </c>
       <c r="I372" s="7"/>
     </row>
-    <row r="373" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="373" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A373" s="1">
         <v>39417</v>
       </c>
@@ -11454,7 +11268,7 @@
       </c>
       <c r="I373" s="7"/>
     </row>
-    <row r="374" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="374" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A374" s="1">
         <v>39448</v>
       </c>
@@ -11481,7 +11295,7 @@
       </c>
       <c r="I374" s="7"/>
     </row>
-    <row r="375" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="375" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A375" s="1">
         <v>39479</v>
       </c>
@@ -11508,7 +11322,7 @@
       </c>
       <c r="I375" s="7"/>
     </row>
-    <row r="376" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="376" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A376" s="1">
         <v>39508</v>
       </c>
@@ -11535,7 +11349,7 @@
       </c>
       <c r="I376" s="7"/>
     </row>
-    <row r="377" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="377" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A377" s="1">
         <v>39539</v>
       </c>
@@ -11562,7 +11376,7 @@
       </c>
       <c r="I377" s="7"/>
     </row>
-    <row r="378" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="378" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A378" s="1">
         <v>39569</v>
       </c>
@@ -11589,7 +11403,7 @@
       </c>
       <c r="I378" s="7"/>
     </row>
-    <row r="379" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="379" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A379" s="1">
         <v>39600</v>
       </c>
@@ -11616,7 +11430,7 @@
       </c>
       <c r="I379" s="7"/>
     </row>
-    <row r="380" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="380" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A380" s="1">
         <v>39630</v>
       </c>
@@ -11643,7 +11457,7 @@
       </c>
       <c r="I380" s="7"/>
     </row>
-    <row r="381" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="381" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A381" s="1">
         <v>39661</v>
       </c>
@@ -11670,7 +11484,7 @@
       </c>
       <c r="I381" s="7"/>
     </row>
-    <row r="382" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="382" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A382" s="1">
         <v>39692</v>
       </c>
@@ -11697,7 +11511,7 @@
       </c>
       <c r="I382" s="7"/>
     </row>
-    <row r="383" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="383" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A383" s="1">
         <v>39722</v>
       </c>
@@ -11724,7 +11538,7 @@
       </c>
       <c r="I383" s="7"/>
     </row>
-    <row r="384" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="384" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A384" s="1">
         <v>39753</v>
       </c>
@@ -11751,7 +11565,7 @@
       </c>
       <c r="I384" s="7"/>
     </row>
-    <row r="385" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="385" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A385" s="1">
         <v>39783</v>
       </c>
@@ -11778,7 +11592,7 @@
       </c>
       <c r="I385" s="7"/>
     </row>
-    <row r="386" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="386" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A386" s="1">
         <v>39814</v>
       </c>
@@ -11805,7 +11619,7 @@
       </c>
       <c r="I386" s="7"/>
     </row>
-    <row r="387" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="387" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A387" s="1">
         <v>39845</v>
       </c>
@@ -11832,7 +11646,7 @@
       </c>
       <c r="I387" s="7"/>
     </row>
-    <row r="388" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="388" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A388" s="1">
         <v>39873</v>
       </c>
@@ -11859,7 +11673,7 @@
       </c>
       <c r="I388" s="7"/>
     </row>
-    <row r="389" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="389" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A389" s="1">
         <v>39904</v>
       </c>
@@ -11886,7 +11700,7 @@
       </c>
       <c r="I389" s="7"/>
     </row>
-    <row r="390" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="390" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A390" s="1">
         <v>39934</v>
       </c>
@@ -11913,7 +11727,7 @@
       </c>
       <c r="I390" s="7"/>
     </row>
-    <row r="391" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="391" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A391" s="1">
         <v>39965</v>
       </c>
@@ -11940,7 +11754,7 @@
       </c>
       <c r="I391" s="7"/>
     </row>
-    <row r="392" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="392" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A392" s="1">
         <v>39995</v>
       </c>
@@ -11967,7 +11781,7 @@
       </c>
       <c r="I392" s="7"/>
     </row>
-    <row r="393" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="393" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A393" s="1">
         <v>40026</v>
       </c>
@@ -11994,7 +11808,7 @@
       </c>
       <c r="I393" s="7"/>
     </row>
-    <row r="394" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="394" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A394" s="1">
         <v>40057</v>
       </c>
@@ -12021,7 +11835,7 @@
       </c>
       <c r="I394" s="7"/>
     </row>
-    <row r="395" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="395" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A395" s="1">
         <v>40087</v>
       </c>
@@ -12048,7 +11862,7 @@
       </c>
       <c r="I395" s="7"/>
     </row>
-    <row r="396" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="396" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A396" s="1">
         <v>40118</v>
       </c>
@@ -12075,7 +11889,7 @@
       </c>
       <c r="I396" s="7"/>
     </row>
-    <row r="397" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="397" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A397" s="1">
         <v>40148</v>
       </c>
@@ -12102,7 +11916,7 @@
       </c>
       <c r="I397" s="7"/>
     </row>
-    <row r="398" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="398" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A398" s="1">
         <v>40179</v>
       </c>
@@ -12129,7 +11943,7 @@
       </c>
       <c r="I398" s="7"/>
     </row>
-    <row r="399" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="399" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A399" s="1">
         <v>40210</v>
       </c>
@@ -12156,7 +11970,7 @@
       </c>
       <c r="I399" s="7"/>
     </row>
-    <row r="400" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="400" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A400" s="1">
         <v>40238</v>
       </c>
@@ -12183,7 +11997,7 @@
       </c>
       <c r="I400" s="7"/>
     </row>
-    <row r="401" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="401" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A401" s="1">
         <v>40269</v>
       </c>
@@ -12210,7 +12024,7 @@
       </c>
       <c r="I401" s="7"/>
     </row>
-    <row r="402" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="402" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A402" s="1">
         <v>40299</v>
       </c>
@@ -12237,7 +12051,7 @@
       </c>
       <c r="I402" s="7"/>
     </row>
-    <row r="403" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="403" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A403" s="1">
         <v>40330</v>
       </c>
@@ -12264,7 +12078,7 @@
       </c>
       <c r="I403" s="7"/>
     </row>
-    <row r="404" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="404" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A404" s="1">
         <v>40360</v>
       </c>
@@ -12291,7 +12105,7 @@
       </c>
       <c r="I404" s="7"/>
     </row>
-    <row r="405" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="405" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A405" s="1">
         <v>40391</v>
       </c>
@@ -12318,7 +12132,7 @@
       </c>
       <c r="I405" s="7"/>
     </row>
-    <row r="406" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="406" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A406" s="1">
         <v>40422</v>
       </c>
@@ -12345,7 +12159,7 @@
       </c>
       <c r="I406" s="7"/>
     </row>
-    <row r="407" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="407" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A407" s="1">
         <v>40452</v>
       </c>
@@ -12372,7 +12186,7 @@
       </c>
       <c r="I407" s="7"/>
     </row>
-    <row r="408" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="408" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A408" s="1">
         <v>40483</v>
       </c>
@@ -12399,7 +12213,7 @@
       </c>
       <c r="I408" s="7"/>
     </row>
-    <row r="409" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="409" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A409" s="1">
         <v>40513</v>
       </c>
@@ -12426,7 +12240,7 @@
       </c>
       <c r="I409" s="7"/>
     </row>
-    <row r="410" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="410" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A410" s="1">
         <v>40544</v>
       </c>
@@ -12453,7 +12267,7 @@
       </c>
       <c r="I410" s="7"/>
     </row>
-    <row r="411" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="411" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A411" s="1">
         <v>40575</v>
       </c>
@@ -12480,7 +12294,7 @@
       </c>
       <c r="I411" s="7"/>
     </row>
-    <row r="412" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="412" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A412" s="1">
         <v>40603</v>
       </c>
@@ -12507,7 +12321,7 @@
       </c>
       <c r="I412" s="7"/>
     </row>
-    <row r="413" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="413" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A413" s="1">
         <v>40634</v>
       </c>
@@ -12534,7 +12348,7 @@
       </c>
       <c r="I413" s="7"/>
     </row>
-    <row r="414" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="414" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A414" s="1">
         <v>40664</v>
       </c>
@@ -12561,7 +12375,7 @@
       </c>
       <c r="I414" s="7"/>
     </row>
-    <row r="415" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="415" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A415" s="1">
         <v>40695</v>
       </c>
@@ -12588,7 +12402,7 @@
       </c>
       <c r="I415" s="7"/>
     </row>
-    <row r="416" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="416" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A416" s="1">
         <v>40725</v>
       </c>
@@ -12615,7 +12429,7 @@
       </c>
       <c r="I416" s="7"/>
     </row>
-    <row r="417" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="417" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A417" s="1">
         <v>40756</v>
       </c>
@@ -12642,7 +12456,7 @@
       </c>
       <c r="I417" s="7"/>
     </row>
-    <row r="418" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="418" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A418" s="1">
         <v>40787</v>
       </c>
@@ -12669,7 +12483,7 @@
       </c>
       <c r="I418" s="7"/>
     </row>
-    <row r="419" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="419" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A419" s="1">
         <v>40817</v>
       </c>
@@ -12696,7 +12510,7 @@
       </c>
       <c r="I419" s="7"/>
     </row>
-    <row r="420" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="420" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A420" s="1">
         <v>40848</v>
       </c>
@@ -12723,7 +12537,7 @@
       </c>
       <c r="I420" s="7"/>
     </row>
-    <row r="421" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="421" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A421" s="1">
         <v>40878</v>
       </c>
@@ -12750,7 +12564,7 @@
       </c>
       <c r="I421" s="7"/>
     </row>
-    <row r="422" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="422" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A422" s="1">
         <v>40909</v>
       </c>
@@ -12777,7 +12591,7 @@
       </c>
       <c r="I422" s="7"/>
     </row>
-    <row r="423" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="423" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A423" s="1">
         <v>40940</v>
       </c>
@@ -12804,7 +12618,7 @@
       </c>
       <c r="I423" s="7"/>
     </row>
-    <row r="424" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="424" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A424" s="1">
         <v>40969</v>
       </c>
@@ -12831,7 +12645,7 @@
       </c>
       <c r="I424" s="7"/>
     </row>
-    <row r="425" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="425" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A425" s="1">
         <v>41000</v>
       </c>
@@ -12858,7 +12672,7 @@
       </c>
       <c r="I425" s="7"/>
     </row>
-    <row r="426" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="426" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A426" s="1">
         <v>41030</v>
       </c>
@@ -12885,7 +12699,7 @@
       </c>
       <c r="I426" s="7"/>
     </row>
-    <row r="427" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="427" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A427" s="1">
         <v>41061</v>
       </c>
@@ -12912,7 +12726,7 @@
       </c>
       <c r="I427" s="7"/>
     </row>
-    <row r="428" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="428" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A428" s="1">
         <v>41091</v>
       </c>
@@ -12939,7 +12753,7 @@
       </c>
       <c r="I428" s="7"/>
     </row>
-    <row r="429" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="429" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A429" s="1">
         <v>41122</v>
       </c>
@@ -12966,7 +12780,7 @@
       </c>
       <c r="I429" s="7"/>
     </row>
-    <row r="430" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="430" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A430" s="1">
         <v>41153</v>
       </c>
@@ -12993,7 +12807,7 @@
       </c>
       <c r="I430" s="7"/>
     </row>
-    <row r="431" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="431" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A431" s="1">
         <v>41183</v>
       </c>
@@ -13020,7 +12834,7 @@
       </c>
       <c r="I431" s="7"/>
     </row>
-    <row r="432" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="432" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A432" s="1">
         <v>41214</v>
       </c>
@@ -13047,7 +12861,7 @@
       </c>
       <c r="I432" s="7"/>
     </row>
-    <row r="433" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="433" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A433" s="1">
         <v>41244</v>
       </c>
@@ -13074,7 +12888,7 @@
       </c>
       <c r="I433" s="7"/>
     </row>
-    <row r="434" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="434" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A434" s="1">
         <v>41275</v>
       </c>
@@ -13101,7 +12915,7 @@
       </c>
       <c r="I434" s="7"/>
     </row>
-    <row r="435" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="435" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A435" s="1">
         <v>41306</v>
       </c>
@@ -13128,7 +12942,7 @@
       </c>
       <c r="I435" s="7"/>
     </row>
-    <row r="436" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="436" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A436" s="1">
         <v>41334</v>
       </c>
@@ -13155,7 +12969,7 @@
       </c>
       <c r="I436" s="7"/>
     </row>
-    <row r="437" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="437" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A437" s="1">
         <v>41365</v>
       </c>
@@ -13182,7 +12996,7 @@
       </c>
       <c r="I437" s="7"/>
     </row>
-    <row r="438" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="438" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A438" s="1">
         <v>41395</v>
       </c>
@@ -13209,7 +13023,7 @@
       </c>
       <c r="I438" s="7"/>
     </row>
-    <row r="439" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="439" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A439" s="1">
         <v>41426</v>
       </c>
@@ -13236,7 +13050,7 @@
       </c>
       <c r="I439" s="7"/>
     </row>
-    <row r="440" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="440" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A440" s="1">
         <v>41456</v>
       </c>
@@ -13263,7 +13077,7 @@
       </c>
       <c r="I440" s="7"/>
     </row>
-    <row r="441" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="441" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A441" s="1">
         <v>41487</v>
       </c>
@@ -13290,7 +13104,7 @@
       </c>
       <c r="I441" s="7"/>
     </row>
-    <row r="442" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="442" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A442" s="1">
         <v>41518</v>
       </c>
@@ -13317,7 +13131,7 @@
       </c>
       <c r="I442" s="7"/>
     </row>
-    <row r="443" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="443" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A443" s="1">
         <v>41548</v>
       </c>
@@ -13344,7 +13158,7 @@
       </c>
       <c r="I443" s="7"/>
     </row>
-    <row r="444" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="444" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A444" s="1">
         <v>41579</v>
       </c>
@@ -13371,7 +13185,7 @@
       </c>
       <c r="I444" s="7"/>
     </row>
-    <row r="445" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="445" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A445" s="1">
         <v>41609</v>
       </c>
